--- a/Worker_Verticality/monitoring_mitratel_hourly.xlsx
+++ b/Worker_Verticality/monitoring_mitratel_hourly.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-16" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -106,7 +107,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -201,6 +202,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F9FAFB"/>
         <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -371,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -450,6 +457,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3389,4 +3405,1699 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Nama Site</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Site Code</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>Client ID</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>PEDURENANMUSTIKAJAYA</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>CKR-04-181</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PEDURENAN</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>JABODETABEK</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>JALANMUSTIKASARI</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>BKS-04-079</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_JALANMUSTIKA</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>JABODETABEK</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>SMU84</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>GGP-04-196</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_SMU84</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>JABODETABEK</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>SWADAYA</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>CKG-04-367</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_SWADAYA</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>JABODETABEK</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>BEKASI_KOTA</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>BKS-04-194</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_BEKASIKOTA</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>JABODETABEK</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>GANGAMBONTANGERANG</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>TNG-04-080</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_GANGAM</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>JABODETABEK</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>PERMANENISASICIOKONGSUKARESIKSIDAMULIH</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>CMS-05-279</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PEMRANEN</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>JABAR</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>KERTAMUKTI-CIKONDANG</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>SPA-05-017</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_KERTAMUKTI</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>JABAR</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>JLABDULSALEH-SETIARATUTSK</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>TSM-05-022</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_JLABDULSALEH</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>JABAR</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>BANTARSARI-CIEUNTEUNG</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>BDG-05-625</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_BANTARSARI</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>JABAR</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Jalan Anggrek Siitu</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>SMD-05-035</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_SIITU</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>JABAR</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Rnc_Karmul2_part2_Site Planning 1_NewSite_120</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>SPA-05-085</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_KARMUL</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>JABAR</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Karangboyo Cepu</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>BLA-06-015</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_KARANGBOYO</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Karangjati Indah</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>BTL-06-034</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_KARANGJATI</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>PASIR KIDUL BANYUMAS</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>PWT-06-046</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PASIRKIDUL</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>PODOSUGIH</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>PKL-06-025</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_PODOSUGIH</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>BANJARSARI_PEDALANGAN</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>SMG-06-366</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PEDALANGAN</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Letjend S Parman Ungaran</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>CLP-06-058</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_UNGARAN</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Palebon tengah</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>BYL-06-122</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PELEBON</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>MARGODADI</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>SMN-06-114</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_MARGODADI</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>JATENG</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>GanggangPanjang</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>SDA-07-036</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_GANGGANG</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>JATIM</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>MANGUNSARKORO 3</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>TRK-07-024</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_GAYUNGSARI</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>JATIM</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>GAYUNG_SARI_BARAT-JAMBANGAN</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>SBY-07-645</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_GAYUNG</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>JATIM</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>SEPANDECANDI2DMT</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>SDA-07-078</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_SEPANDE</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>JATIM</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>BUKITRAYASEPAKU</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>PNJ-09-044</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_BUKITRAYASEPAKU</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Kalimantan</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>DMT_NEW_IKN</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>PNJ-09-036</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_DMTNEWIKN</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>Kalimantan</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>DMT ISAT_Tamangapa</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>SULAWESI</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_ISATTAMANGAPA</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>SULAWESI</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Al Yusro PKP</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>PGP-03-007</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_ALYUSRO</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Perumnas Salemba</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>PGP-03-054</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PERUMSALEM</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>GIRIMAYA</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>PGP-03-059</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_GIRIMAYA</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Suak Permai</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-010</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_SUAKPERMAI</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>SUKA MULYA PLG</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-096</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_SUKAMULYA</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Keluarga PLG</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-106</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_KELUARGAPLG</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Lubuk Kawah PLG</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-107</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_LUBUKAWAH</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Arimbi PLG</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-108</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_ARIMBI</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Jalan BSD PLG</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-109</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_JLNBSDPLG</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Jalan Jepang PLG</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-112</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_JLNJPNPLG</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Gaya Baru PLG</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-118</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_GAYABARUPLG</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Lorong Pancasila PLG</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-120</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_LOPANCAPLG</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>Sentosa 2 PLG</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-121</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_SANTOSA2PLG</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>16 Ulu PLG</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-128</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_16ULUPLG</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>Lorong Depok PLG</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-131</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_LODEPOKPLG</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>Mataram Kertapati</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-132</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_MATARAM</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>KOMPLEK_PMD-SEDUDUK_PUTIH</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-387</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_SEDUDUK</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>SUKABANGUN2</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>PLG-03-398</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_SUKABANGUN</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Ketuan Jaya</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>PLG-03-040</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_KETUANJAYA</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>PEMBANGUNAN BDL</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>BDL-03-064</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PEMBANGUNAN</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGSEL</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>SIMPANG TALUAK</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>PBR-02-482</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_TALUAK</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>PARIAMAN 6</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
+        <is>
+          <t>BTM-02-493</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PARIAMAN6</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>DESA_HARAPAN</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>BLS-02-175</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_DESAHARAPAN</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>DUMAI 9</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>DUM-02-037</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_DUMAI9</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>BSK 3</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>BSK-02-015</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_BSK3</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Lenggini 3</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="inlineStr">
+        <is>
+          <t>BKN-02-035</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_LENGGINI3</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>SMAS CENDANA</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>BLS-02-054</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_SMASCENDANA</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Sudirman Bengkalis</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>BLS-02-056</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_BENGKALIS</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>Raden Patah (reloc)</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>BTM-02-114</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_RADENPATAH</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>PADANG PASIR POI</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>PAD-02-092</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_PASIRPOI</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>GANTING PARAK 2</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>PAD-02-091</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_PARAK</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGTENG</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>Dagang Kelambir</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>LBP-01-128</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_DAKELAMBIR</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGUT</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>PELAB AJIBATA</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>PRR-01-004</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>E32_VER_PELABAJIBATA</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>SUMBAGUT</t>
+        </is>
+      </c>
+      <c r="E61" s="21" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>Komplek Sejahtera</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
+        <is>
+          <t>MDN-01-097</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>E32_VER_KOSEJAHTERA</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>SUMBAGUT</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>OFFLINE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>